--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.79027</v>
+        <v>16.9298</v>
       </c>
       <c r="D2" t="n">
-        <v>16.95837</v>
+        <v>16.76865</v>
       </c>
       <c r="E2" t="n">
-        <v>17.09944</v>
+        <v>16.8199</v>
       </c>
       <c r="F2" t="n">
-        <v>43.2836</v>
+        <v>42.82775</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05132</v>
+        <v>0.05102</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80712</v>
+        <v>1.81129</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.92659</v>
+        <v>16.94587</v>
       </c>
       <c r="D3" t="n">
-        <v>16.63289</v>
+        <v>16.6692</v>
       </c>
       <c r="E3" t="n">
-        <v>17.18952</v>
+        <v>16.88083</v>
       </c>
       <c r="F3" t="n">
-        <v>42.26425</v>
+        <v>41.71137</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05068</v>
+        <v>0.05018</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86155</v>
+        <v>1.85112</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.07202</v>
+        <v>17.03397</v>
       </c>
       <c r="D4" t="n">
-        <v>16.76926</v>
+        <v>16.45528</v>
       </c>
       <c r="E4" t="n">
-        <v>16.9169</v>
+        <v>16.60676</v>
       </c>
       <c r="F4" t="n">
-        <v>43.64444</v>
+        <v>42.46228</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05136</v>
+        <v>0.05087</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82499</v>
+        <v>1.87842</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.78157</v>
+        <v>17.22323</v>
       </c>
       <c r="D6" t="n">
-        <v>15.97072</v>
+        <v>16.20236</v>
       </c>
       <c r="E6" t="n">
-        <v>16.3342</v>
+        <v>16.44355</v>
       </c>
       <c r="F6" t="n">
-        <v>21.4963</v>
+        <v>21.3487</v>
       </c>
       <c r="G6" t="n">
-        <v>34.0682</v>
+        <v>33.60032</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.70995</v>
+        <v>16.95132</v>
       </c>
       <c r="D7" t="n">
-        <v>15.74772</v>
+        <v>16.11665</v>
       </c>
       <c r="E7" t="n">
-        <v>16.40323</v>
+        <v>16.13849</v>
       </c>
       <c r="F7" t="n">
-        <v>21.64147</v>
+        <v>21.96464</v>
       </c>
       <c r="G7" t="n">
-        <v>34.82602</v>
+        <v>34.44519</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.05722</v>
+        <v>16.77962</v>
       </c>
       <c r="D8" t="n">
-        <v>16.01904</v>
+        <v>15.5968</v>
       </c>
       <c r="E8" t="n">
-        <v>16.17639</v>
+        <v>16.77047</v>
       </c>
       <c r="F8" t="n">
-        <v>22.216</v>
+        <v>22.01556</v>
       </c>
       <c r="G8" t="n">
-        <v>34.21448</v>
+        <v>34.95828</v>
       </c>
     </row>
   </sheetData>
